--- a/artfynd/A 40022-2024 artfynd.xlsx
+++ b/artfynd/A 40022-2024 artfynd.xlsx
@@ -777,6 +777,11 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>Kjell Ek</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
@@ -894,6 +899,11 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>Kjell Ek</t>
+        </is>
+      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>

--- a/artfynd/A 40022-2024 artfynd.xlsx
+++ b/artfynd/A 40022-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127394473</v>
       </c>
       <c r="B2" t="n">
-        <v>56525</v>
+        <v>56529</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>127394555</v>
       </c>
       <c r="B3" t="n">
-        <v>56544</v>
+        <v>56548</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>123925645</v>
       </c>
       <c r="B4" t="n">
-        <v>57815</v>
+        <v>57819</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 40022-2024 artfynd.xlsx
+++ b/artfynd/A 40022-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127394473</v>
       </c>
       <c r="B2" t="n">
-        <v>56529</v>
+        <v>56531</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>127394555</v>
       </c>
       <c r="B3" t="n">
-        <v>56548</v>
+        <v>56550</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>123925645</v>
       </c>
       <c r="B4" t="n">
-        <v>57819</v>
+        <v>57821</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 40022-2024 artfynd.xlsx
+++ b/artfynd/A 40022-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127394473</v>
       </c>
       <c r="B2" t="n">
-        <v>56531</v>
+        <v>56534</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>127394555</v>
       </c>
       <c r="B3" t="n">
-        <v>56550</v>
+        <v>56553</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>123925645</v>
       </c>
       <c r="B4" t="n">
-        <v>57821</v>
+        <v>57824</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 40022-2024 artfynd.xlsx
+++ b/artfynd/A 40022-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127394473</v>
       </c>
       <c r="B2" t="n">
-        <v>56534</v>
+        <v>56540</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>127394555</v>
       </c>
       <c r="B3" t="n">
-        <v>56553</v>
+        <v>56559</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>123925645</v>
       </c>
       <c r="B4" t="n">
-        <v>57824</v>
+        <v>57830</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 40022-2024 artfynd.xlsx
+++ b/artfynd/A 40022-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127394473</v>
+        <v>128125017</v>
       </c>
       <c r="B2" t="n">
-        <v>56540</v>
+        <v>56547</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>205998</v>
+        <v>205992</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -745,22 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-05-17</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>22:21</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-05-17</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>22:21</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -797,32 +787,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127394555</v>
+        <v>127394473</v>
       </c>
       <c r="B3" t="n">
-        <v>56559</v>
+        <v>56540</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -867,27 +857,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-05-18</t>
+          <t>2025-05-17</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>02:53</t>
+          <t>22:21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-05-18</t>
+          <t>2025-05-17</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>02:53</t>
+          <t>22:21</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Batlogger S2  Validerad av Kjell Ek</t>
+          <t>Batlogger S2 Validerad av Kjell Ek</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -919,49 +909,50 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123925645</v>
+        <v>127394555</v>
       </c>
       <c r="B4" t="n">
-        <v>57830</v>
+        <v>56559</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103020</v>
+        <v>205995</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stocken 2:63 sydöstra skogsbrynet, Hl</t>
+          <t>Stocken 2:63 sydvästra skogsbrynet, Löftaskog, Stråvalla, Hl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>330558</v>
+        <v>330522</v>
       </c>
       <c r="R4" t="n">
-        <v>6355128</v>
+        <v>6355173</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -988,22 +979,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-04-09</t>
+          <t>2025-05-18</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>02:53</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-04-09</t>
+          <t>2025-05-18</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>02:53</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Batlogger S2  Validerad av Kjell Ek</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1015,6 +1011,11 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>Kjell Ek</t>
+        </is>
+      </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
@@ -1027,6 +1028,117 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>123925645</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57830</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Stocken 2:63 sydöstra skogsbrynet, Hl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>330558</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6355128</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Varberg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Stråvalla</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Linda Frank</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Linda Frank</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 40022-2024 artfynd.xlsx
+++ b/artfynd/A 40022-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128125017</v>
       </c>
       <c r="B2" t="n">
-        <v>56547</v>
+        <v>56559</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40022-2024 artfynd.xlsx
+++ b/artfynd/A 40022-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1140,6 +1140,850 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128627848</v>
+      </c>
+      <c r="B6" t="n">
+        <v>56559</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>205992</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vattenfladdermus</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Myotis daubentonii</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Kuhl, 1817)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Stocken 2:63 nordvästra skogsbrynet, Löftaskog, Stråvalla, Hl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>330554</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6355271</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Varberg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Stråvalla</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>23:28</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>23:28</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Batlogger S2 Validerad av Kjell Ek, Varberg</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>Kjell Ek</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Linda Frank</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Linda Frank</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128627789</v>
+      </c>
+      <c r="B7" t="n">
+        <v>56552</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Stocken 2:63 skogsgläntan, Löftaskog, Stråvalla, Hl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>330531</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6355249</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Varberg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Stråvalla</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Batlogger S2 Validerad av Kjell Ek, Varberg</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>Kjell Ek</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Linda Frank</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Linda Frank</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128627722</v>
+      </c>
+      <c r="B8" t="n">
+        <v>56573</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>206002</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Brunlångöra</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Plecotus auritus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Stocken 2:63 skogsgläntan, Löftaskog, Stråvalla, Hl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>330531</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6355249</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Varberg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Stråvalla</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>00:35</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>00:35</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Batlogger S2 Validerad av Kjell Ek, Varberg</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>Kjell Ek</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Linda Frank</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Linda Frank</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128627732</v>
+      </c>
+      <c r="B9" t="n">
+        <v>56571</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>205995</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Pipistrellus pygmaeus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Stocken 2:63 skogsgläntan, Löftaskog, Stråvalla, Hl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>330531</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6355249</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Varberg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Stråvalla</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>04:03</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>04:03</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Batlogger S2 Validerad av Kjell Ek, Varberg</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>Kjell Ek</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Linda Frank</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Linda Frank</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128627695</v>
+      </c>
+      <c r="B10" t="n">
+        <v>56559</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>205992</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Vattenfladdermus</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Myotis daubentonii</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Kuhl, 1817)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Stocken 2:63 skogsgläntan, Löftaskog, Stråvalla, Hl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>330531</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6355249</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Varberg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Stråvalla</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>22:40</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>22:40</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Batlogger S2 Validerad av Kjell Ek, Varberg</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>Kjell Ek</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Linda Frank</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Linda Frank</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>128627855</v>
+      </c>
+      <c r="B11" t="n">
+        <v>56552</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Stocken 2:63 nordvästra skogsbrynet, Löftaskog, Stråvalla, Hl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>330554</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6355271</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Varberg</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Stråvalla</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-06-22</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>01:50</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-06-22</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>01:50</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Batlogger S2 Validerad av Kjell Ek, Varberg</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>Kjell Ek</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Linda Frank</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Linda Frank</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>128627868</v>
+      </c>
+      <c r="B12" t="n">
+        <v>56571</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>205995</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Pipistrellus pygmaeus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Stocken 2:63 nordvästra skogsbrynet, Löftaskog, Stråvalla, Hl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>330554</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6355271</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Varberg</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Stråvalla</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-06-22</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>03:01</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-06-22</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>03:01</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Batlogger S2 Validerad av Kjell Ek, Varberg</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>Kjell Ek</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Linda Frank</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Linda Frank</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 40022-2024 artfynd.xlsx
+++ b/artfynd/A 40022-2024 artfynd.xlsx
@@ -1145,7 +1145,7 @@
         <v>128627848</v>
       </c>
       <c r="B6" t="n">
-        <v>56559</v>
+        <v>56563</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
         <v>128627789</v>
       </c>
       <c r="B7" t="n">
-        <v>56552</v>
+        <v>56556</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>128627722</v>
       </c>
       <c r="B8" t="n">
-        <v>56573</v>
+        <v>56577</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>128627732</v>
       </c>
       <c r="B9" t="n">
-        <v>56571</v>
+        <v>56575</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1623,7 +1623,7 @@
         <v>128627695</v>
       </c>
       <c r="B10" t="n">
-        <v>56559</v>
+        <v>56563</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>128627855</v>
       </c>
       <c r="B11" t="n">
-        <v>56552</v>
+        <v>56556</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         <v>128627868</v>
       </c>
       <c r="B12" t="n">
-        <v>56571</v>
+        <v>56575</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 40022-2024 artfynd.xlsx
+++ b/artfynd/A 40022-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128125017</v>
       </c>
       <c r="B2" t="n">
-        <v>56559</v>
+        <v>56563</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40022-2024 artfynd.xlsx
+++ b/artfynd/A 40022-2024 artfynd.xlsx
@@ -1145,7 +1145,7 @@
         <v>128627848</v>
       </c>
       <c r="B6" t="n">
-        <v>56563</v>
+        <v>56590</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
         <v>128627789</v>
       </c>
       <c r="B7" t="n">
-        <v>56556</v>
+        <v>56583</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>128627722</v>
       </c>
       <c r="B8" t="n">
-        <v>56577</v>
+        <v>56604</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>128627732</v>
       </c>
       <c r="B9" t="n">
-        <v>56575</v>
+        <v>56602</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1623,7 +1623,7 @@
         <v>128627695</v>
       </c>
       <c r="B10" t="n">
-        <v>56563</v>
+        <v>56590</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>128627855</v>
       </c>
       <c r="B11" t="n">
-        <v>56556</v>
+        <v>56583</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         <v>128627868</v>
       </c>
       <c r="B12" t="n">
-        <v>56575</v>
+        <v>56602</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 40022-2024 artfynd.xlsx
+++ b/artfynd/A 40022-2024 artfynd.xlsx
@@ -1145,7 +1145,7 @@
         <v>128627848</v>
       </c>
       <c r="B6" t="n">
-        <v>56590</v>
+        <v>56593</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
         <v>128627789</v>
       </c>
       <c r="B7" t="n">
-        <v>56583</v>
+        <v>56586</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>128627722</v>
       </c>
       <c r="B8" t="n">
-        <v>56604</v>
+        <v>56607</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>128627732</v>
       </c>
       <c r="B9" t="n">
-        <v>56602</v>
+        <v>56605</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1623,7 +1623,7 @@
         <v>128627695</v>
       </c>
       <c r="B10" t="n">
-        <v>56590</v>
+        <v>56593</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>128627855</v>
       </c>
       <c r="B11" t="n">
-        <v>56583</v>
+        <v>56586</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         <v>128627868</v>
       </c>
       <c r="B12" t="n">
-        <v>56602</v>
+        <v>56605</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 40022-2024 artfynd.xlsx
+++ b/artfynd/A 40022-2024 artfynd.xlsx
@@ -1145,7 +1145,7 @@
         <v>128627848</v>
       </c>
       <c r="B6" t="n">
-        <v>56593</v>
+        <v>56596</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
         <v>128627789</v>
       </c>
       <c r="B7" t="n">
-        <v>56586</v>
+        <v>56589</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>128627722</v>
       </c>
       <c r="B8" t="n">
-        <v>56607</v>
+        <v>56610</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>128627732</v>
       </c>
       <c r="B9" t="n">
-        <v>56605</v>
+        <v>56608</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1623,7 +1623,7 @@
         <v>128627695</v>
       </c>
       <c r="B10" t="n">
-        <v>56593</v>
+        <v>56596</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>128627855</v>
       </c>
       <c r="B11" t="n">
-        <v>56586</v>
+        <v>56589</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         <v>128627868</v>
       </c>
       <c r="B12" t="n">
-        <v>56605</v>
+        <v>56608</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 40022-2024 artfynd.xlsx
+++ b/artfynd/A 40022-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128125017</v>
+        <v>121334798</v>
       </c>
       <c r="B2" t="n">
-        <v>56563</v>
+        <v>96458</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,42 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>205992</v>
+        <v>2818</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Stocken 2:63 sydvästra skogsbrynet, Löftaskog, Stråvalla, Hl</t>
+          <t>Löftaskog, Hl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>330522</v>
+        <v>330506</v>
       </c>
       <c r="R2" t="n">
-        <v>6355173</v>
+        <v>6355104</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,17 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2024-10-23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2024-10-23</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Batlogger S2 Validerad av Kjell Ek</t>
+          <t>Detta fynd är noterat under en NVI med projektkod JMN0144 utförd 2024 av Calluna AB.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -766,74 +761,68 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>Kjell Ek</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Linda Frank</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Linda Frank</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Robin Karlsson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Calluna AB: NVI JMN0144 Löftabro &amp; Löftaskog 2024</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127394473</v>
+        <v>123925913</v>
       </c>
       <c r="B3" t="n">
-        <v>56540</v>
+        <v>57247</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>205998</v>
+        <v>100038</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Stocken 2:63 sydvästra skogsbrynet, Löftaskog, Stråvalla, Hl</t>
+          <t>Stocken 2:63 sydöstra skogsbrynet, Stocken 2:63 sydöstra skogsbrynet, Hl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>330522</v>
+        <v>330552</v>
       </c>
       <c r="R3" t="n">
-        <v>6355173</v>
+        <v>6355137</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,27 +846,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-05-17</t>
+          <t>2025-04-09</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>22:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-05-17</t>
+          <t>2025-04-09</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>22:21</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Batlogger S2 Validerad av Kjell Ek</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -888,11 +872,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>Kjell Ek</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -909,50 +888,49 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127394555</v>
+        <v>123925645</v>
       </c>
       <c r="B4" t="n">
-        <v>56559</v>
+        <v>58112</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>205995</v>
+        <v>103020</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stocken 2:63 sydvästra skogsbrynet, Löftaskog, Stråvalla, Hl</t>
+          <t>Stocken 2:63 sydöstra skogsbrynet, Hl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>330522</v>
+        <v>330558</v>
       </c>
       <c r="R4" t="n">
-        <v>6355173</v>
+        <v>6355128</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -979,27 +957,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-05-18</t>
+          <t>2025-04-09</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>02:53</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-05-18</t>
+          <t>2025-04-09</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>02:53</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Batlogger S2  Validerad av Kjell Ek</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1010,11 +983,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>Kjell Ek</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1031,49 +999,50 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123925645</v>
+        <v>122795492</v>
       </c>
       <c r="B5" t="n">
-        <v>57830</v>
+        <v>56823</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103020</v>
+        <v>205992</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Stocken 2:63 sydöstra skogsbrynet, Hl</t>
+          <t>Stocken 2:63 sydvästra skogsbrynet, Löftaskog, Stråvalla, Hl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>330558</v>
+        <v>330522</v>
       </c>
       <c r="R5" t="n">
-        <v>6355128</v>
+        <v>6355173</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1100,22 +1069,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-04-09</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-04-09</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>01:00</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Registrerad med BatLogger, validerad av Kjell Ek, Varberg.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1142,10 +1116,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128627848</v>
+        <v>122795525</v>
       </c>
       <c r="B6" t="n">
-        <v>56596</v>
+        <v>56823</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1178,17 +1152,17 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Stocken 2:63 nordvästra skogsbrynet, Löftaskog, Stråvalla, Hl</t>
+          <t>Stocken 2:63 sydöstra skogsbrynet, Hl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>330554</v>
+        <v>330558</v>
       </c>
       <c r="R6" t="n">
-        <v>6355271</v>
+        <v>6355128</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1212,27 +1186,27 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-06-21</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-06-21</t>
+          <t>2024-08-03</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Batlogger S2 Validerad av Kjell Ek, Varberg</t>
+          <t>Registrerad med BatLogger, validerad av Kjell Ek, Varberg.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1243,11 +1217,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>Kjell Ek</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1264,32 +1233,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128627789</v>
+        <v>128627695</v>
       </c>
       <c r="B7" t="n">
-        <v>56589</v>
+        <v>56823</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>205998</v>
+        <v>205992</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1334,12 +1303,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>22:40</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>22:40</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1376,32 +1355,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128627722</v>
+        <v>128627848</v>
       </c>
       <c r="B8" t="n">
-        <v>56610</v>
+        <v>56823</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>206002</v>
+        <v>205992</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1412,14 +1391,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Stocken 2:63 skogsgläntan, Löftaskog, Stråvalla, Hl</t>
+          <t>Stocken 2:63 nordvästra skogsbrynet, Löftaskog, Stråvalla, Hl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>330531</v>
+        <v>330554</v>
       </c>
       <c r="R8" t="n">
-        <v>6355249</v>
+        <v>6355271</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1446,22 +1425,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-21</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>00:35</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-21</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>00:35</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1498,10 +1477,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128627732</v>
+        <v>122795487</v>
       </c>
       <c r="B9" t="n">
-        <v>56608</v>
+        <v>56835</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1534,17 +1513,17 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Stocken 2:63 skogsgläntan, Löftaskog, Stråvalla, Hl</t>
+          <t>Stocken 2:63 sydvästra skogsbrynet, Löftaskog, Stråvalla, Hl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>330531</v>
+        <v>330522</v>
       </c>
       <c r="R9" t="n">
-        <v>6355249</v>
+        <v>6355173</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1568,27 +1547,27 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>04:03</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>04:03</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Batlogger S2 Validerad av Kjell Ek, Varberg</t>
+          <t>Registrerad med BatLogger, validerad av Kjell Ek, Varberg.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1599,11 +1578,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AS9" t="inlineStr">
-        <is>
-          <t>Kjell Ek</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1620,10 +1594,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128627695</v>
+        <v>122795523</v>
       </c>
       <c r="B10" t="n">
-        <v>56596</v>
+        <v>56835</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1631,21 +1605,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>205992</v>
+        <v>205995</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1656,17 +1630,17 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Stocken 2:63 skogsgläntan, Löftaskog, Stråvalla, Hl</t>
+          <t>Stocken 2:63 sydöstra skogsbrynet, Hl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>330531</v>
+        <v>330558</v>
       </c>
       <c r="R10" t="n">
-        <v>6355249</v>
+        <v>6355128</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1690,27 +1664,27 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2024-08-03</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Batlogger S2 Validerad av Kjell Ek, Varberg</t>
+          <t>Registrerad med BatLogger, validerad av Kjell Ek, Varberg.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1721,11 +1695,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AS10" t="inlineStr">
-        <is>
-          <t>Kjell Ek</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1742,32 +1711,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128627855</v>
+        <v>128627668</v>
       </c>
       <c r="B11" t="n">
-        <v>56589</v>
+        <v>56835</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1778,14 +1747,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Stocken 2:63 nordvästra skogsbrynet, Löftaskog, Stråvalla, Hl</t>
+          <t>Stocken 2:63 skogsgläntan, Löftaskog, Stråvalla, Hl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>330554</v>
+        <v>330531</v>
       </c>
       <c r="R11" t="n">
-        <v>6355271</v>
+        <v>6355249</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1812,22 +1781,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-06-22</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>01:50</t>
+          <t>03:05</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-06-22</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>01:50</t>
+          <t>03:05</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1867,7 +1836,7 @@
         <v>128627868</v>
       </c>
       <c r="B12" t="n">
-        <v>56608</v>
+        <v>56835</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1984,6 +1953,715 @@
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>122795482</v>
+      </c>
+      <c r="B13" t="n">
+        <v>56816</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Stocken 2:63 sydvästra skogsbrynet, Löftaskog, Stråvalla, Hl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>330522</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6355173</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Varberg</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Stråvalla</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>01:00</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Registrerad med BatLogger, validerad av Kjell Ek, Varberg.</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Linda Frank</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Linda Frank</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>122795520</v>
+      </c>
+      <c r="B14" t="n">
+        <v>56816</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Stocken 2:63 sydöstra skogsbrynet, Hl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>330558</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6355128</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Varberg</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Stråvalla</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>04:00</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Registrerad med BatLogger, validerad av Kjell Ek, Varberg.</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Linda Frank</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Linda Frank</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128595345</v>
+      </c>
+      <c r="B15" t="n">
+        <v>56816</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Stocken 2:63 skogsgläntan, Löftaskog, Stråvalla, Hl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>330531</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6355249</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Varberg</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Stråvalla</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>22:42</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>22:42</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Batlogger S2 Validerad av Kjell Ek, Varberg</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS15" t="inlineStr">
+        <is>
+          <t>Kjell Ek</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Linda Frank</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Linda Frank</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>128627855</v>
+      </c>
+      <c r="B16" t="n">
+        <v>56816</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Stocken 2:63 nordvästra skogsbrynet, Löftaskog, Stråvalla, Hl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>330554</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6355271</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Varberg</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Stråvalla</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-06-22</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>01:50</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-06-22</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>01:50</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Batlogger S2 Validerad av Kjell Ek, Varberg</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS16" t="inlineStr">
+        <is>
+          <t>Kjell Ek</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Linda Frank</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Linda Frank</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>128627722</v>
+      </c>
+      <c r="B17" t="n">
+        <v>56837</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>206002</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Brunlångöra</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Plecotus auritus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Stocken 2:63 skogsgläntan, Löftaskog, Stråvalla, Hl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>330531</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6355249</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Varberg</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Stråvalla</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>00:35</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>00:35</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Batlogger S2 Validerad av Kjell Ek, Varberg</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS17" t="inlineStr">
+        <is>
+          <t>Kjell Ek</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Linda Frank</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Linda Frank</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>116904715</v>
+      </c>
+      <c r="B18" t="n">
+        <v>56689</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>206046</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Älg</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Alces alces</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>gående/springande</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Löftaskog, Hl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>330495</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6355190</v>
+      </c>
+      <c r="S18" t="n">
+        <v>50</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Varberg</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Stråvalla</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-05-07</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-05-07</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Katarina Vartia</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Katarina Vartia</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
